--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488141_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488141_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.991199999999999</v>
+        <v>10.0564</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5757</v>
+        <v>11.4685</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5844</v>
+        <v>-1.4121</v>
       </c>
       <c r="G2" t="n">
         <v>5.931</v>
@@ -610,13 +610,13 @@
         <v>3.891</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7927</v>
+        <v>-0.7275</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.149</v>
+        <v>-0.2561</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6437</v>
+        <v>-0.4713</v>
       </c>
       <c r="V2" t="n">
         <v>1.8883</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0259</v>
+        <v>5.7486</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1935</v>
+        <v>5.6947</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1677</v>
+        <v>0.0539</v>
       </c>
       <c r="G3" t="n">
         <v>6.1751</v>
@@ -688,13 +688,13 @@
         <v>2.594</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7051</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8207</v>
+        <v>-0.3196</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8844</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1962</v>
+        <v>2.003</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0433</v>
+        <v>3.727</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8472</v>
+        <v>-1.724</v>
       </c>
       <c r="G4" t="n">
         <v>0.2977</v>
@@ -766,13 +766,13 @@
         <v>2.7793</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6577</v>
+        <v>0.4645</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6813</v>
+        <v>0.365</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0236</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.3144</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. NDJUNGU</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5354</v>
+        <v>1.6208</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6909999999999999</v>
+        <v>2.2498</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2264</v>
+        <v>-0.629</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2214</v>
+        <v>0.3436</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.3949</v>
+        <v>-1.6655</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1735</v>
+        <v>2.0091</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.122</v>
+        <v>2.0779</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.2169</v>
+        <v>-1.1984</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0949</v>
+        <v>3.2762</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0994</v>
+        <v>-1.7343</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.178</v>
+        <v>-0.4671</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9214</v>
+        <v>-1.2671</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0382</v>
+        <v>1.4823</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4.0763</v>
+        <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8309</v>
+        <v>0.4244</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2114</v>
+        <v>0.1719</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.2524</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8877</v>
+        <v>-0.6294</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2578</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.63</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>J. NDJUNGU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8172</v>
+        <v>1.5643</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3477</v>
+        <v>-1.0712</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5305</v>
+        <v>2.6355</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3436</v>
+        <v>-2.2214</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6655</v>
+        <v>-3.3949</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0091</v>
+        <v>1.1735</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0779</v>
+        <v>-0.122</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1984</v>
+        <v>-2.2169</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2762</v>
+        <v>2.0949</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7343</v>
+        <v>-2.0994</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4671</v>
+        <v>-1.178</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2671</v>
+        <v>-0.9214</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4823</v>
+        <v>2.0382</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4823</v>
+        <v>4.0763</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6208</v>
+        <v>-0.1402</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2699</v>
+        <v>-0.1688</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3509</v>
+        <v>0.0286</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6294</v>
+        <v>1.8877</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2578</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6294</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CABALLERO CARPIO</t>
+          <t>L. DALLACOSTA ORTIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1011</v>
+        <v>0.447</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0547</v>
+        <v>1.8216</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1559</v>
+        <v>-1.3746</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2147</v>
+        <v>-1.1193</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2147</v>
+        <v>-1.8396</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.7202</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2.0246</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.0333</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2147</v>
+        <v>-3.144</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2147</v>
+        <v>-1.8308</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1.3131</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3706</v>
+        <v>2.7793</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3706</v>
+        <v>2.9646</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0547</v>
+        <v>-0.8969</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0547</v>
+        <v>-0.3311</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.5658</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3161</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3133</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. DALLACOSTA ORTIZ</t>
+          <t>S. CABALLERO CARPIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2205</v>
+        <v>0.1011</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2772</v>
+        <v>-0.0547</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4977</v>
+        <v>0.1559</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1193</v>
+        <v>-0.2147</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8396</v>
+        <v>-0.2147</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7202</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0246</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0333</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.144</v>
+        <v>-0.2147</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8308</v>
+        <v>-0.2147</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3131</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7793</v>
+        <v>0.3706</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9646</v>
+        <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5644</v>
+        <v>-0.0547</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8754</v>
+        <v>-0.0547</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6889</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3161</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3133</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4534</v>
+        <v>-1.3002</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0634</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.39</v>
+        <v>-1.2915</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0735</v>
@@ -1234,13 +1234,13 @@
         <v>2.4087</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8061</v>
+        <v>-0.6529</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1131</v>
+        <v>-0.0584</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6929</v>
+        <v>-0.5944</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9444</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6984</v>
+        <v>-2.3991</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9999</v>
+        <v>-1.6514</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6985</v>
+        <v>-0.7477</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4362</v>
@@ -1312,13 +1312,13 @@
         <v>2.594</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8921</v>
+        <v>-0.5929</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.766</v>
+        <v>-0.4175</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1261</v>
+        <v>-0.1754</v>
       </c>
       <c r="V11" t="n">
         <v>0.0005</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.9388</v>
+        <v>18.486</v>
       </c>
       <c r="E12" t="n">
-        <v>22.2725</v>
+        <v>22.8197</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.3337</v>
+        <v>-4.333600000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>8.326400000000001</v>
+        <v>8.3264</v>
       </c>
       <c r="H12" t="n">
         <v>4.2942</v>
@@ -1390,10 +1390,10 @@
         <v>23.1608</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.7057</v>
+        <v>-3.158600000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6163</v>
+        <v>-1.0693</v>
       </c>
       <c r="U12" t="n">
         <v>-2.0892</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.2365</v>
+        <v>6.5751</v>
       </c>
       <c r="E13" t="n">
-        <v>8.6793</v>
+        <v>8.091699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4428</v>
+        <v>-1.5166</v>
       </c>
       <c r="G13" t="n">
         <v>3.0606</v>
@@ -1468,13 +1468,13 @@
         <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6942</v>
+        <v>1.0328</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3779</v>
+        <v>0.7903</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3163</v>
+        <v>0.2425</v>
       </c>
       <c r="V13" t="n">
         <v>0.6289</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.3032</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7365</v>
+        <v>3.5406</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0897</v>
+        <v>-3.2374</v>
       </c>
       <c r="G14" t="n">
         <v>-2.3642</v>
@@ -1546,13 +1546,13 @@
         <v>1.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4932</v>
+        <v>1.1497</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6367</v>
+        <v>0.4409</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8565</v>
+        <v>0.7088</v>
       </c>
       <c r="V14" t="n">
         <v>1.8883</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2919</v>
+        <v>-0.322</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1328</v>
+        <v>-0.161</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1591</v>
+        <v>-0.161</v>
       </c>
       <c r="G15" t="n">
         <v>1.3296</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5002</v>
+        <v>0.8863</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.5071</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6993</v>
+        <v>0.3793</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3144</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6667</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5735</v>
+        <v>2.1797</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.2402</v>
+        <v>-2.8354</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7294</v>
+        <v>3.6256</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3023</v>
+        <v>-0.795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.427</v>
+        <v>4.4206</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0848</v>
+        <v>7.8514</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6748</v>
+        <v>1.2883</v>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>6.5631</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3554</v>
+        <v>-4.2258</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3724</v>
+        <v>-2.0833</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.983</v>
+        <v>-2.1426</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3706</v>
+        <v>-3.891</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-5.5586</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4355</v>
+        <v>-0.0759</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4887</v>
+        <v>-0.1131</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0532</v>
+        <v>0.0373</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.2022</v>
+        <v>-0.3144</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.2022</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9512</v>
+        <v>-1.1569</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1797</v>
+        <v>3.1818</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.1308</v>
+        <v>-4.3387</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6256</v>
+        <v>0.7294</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.795</v>
+        <v>0.3023</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4206</v>
+        <v>0.427</v>
       </c>
       <c r="J17" t="n">
-        <v>7.8514</v>
+        <v>3.0848</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2883</v>
+        <v>1.6748</v>
       </c>
       <c r="L17" t="n">
-        <v>6.5631</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.2258</v>
+        <v>-2.3554</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0833</v>
+        <v>-1.3724</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1426</v>
+        <v>-0.983</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.891</v>
+        <v>0.3706</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.5586</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3713</v>
+        <v>-0.0547</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1131</v>
+        <v>0.097</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2582</v>
+        <v>-0.1517</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3144</v>
+        <v>-2.2022</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3144</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4324</v>
+        <v>-2.2612</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5618</v>
+        <v>-0.3659</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8707</v>
+        <v>-1.8953</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7632</v>
@@ -1858,13 +1858,13 @@
         <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.484</v>
+        <v>-0.3128</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2736</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2104</v>
+        <v>-0.235</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5583</v>
+        <v>-3.1173</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4956</v>
+        <v>-3.1038</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0135</v>
       </c>
       <c r="G19" t="n">
         <v>-2.9029</v>
@@ -1936,13 +1936,13 @@
         <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5442</v>
+        <v>-0.1032</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6566</v>
+        <v>-0.2649</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1124</v>
+        <v>0.1616</v>
       </c>
       <c r="V19" t="n">
         <v>0.63</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4228</v>
+        <v>-4.5951</v>
       </c>
       <c r="E20" t="n">
         <v>-3.2325</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1903</v>
+        <v>-1.3626</v>
       </c>
       <c r="G20" t="n">
         <v>-4.1562</v>
@@ -2014,13 +2014,13 @@
         <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0304</v>
+        <v>0.858</v>
       </c>
       <c r="T20" t="n">
         <v>0.531</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4994</v>
+        <v>0.327</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.6338</v>
+        <v>-5.8974</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5569</v>
+        <v>-1.1652</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.0769</v>
+        <v>-4.7322</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0006</v>
@@ -2092,13 +2092,13 @@
         <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8185</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5807</v>
+        <v>-0.189</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2378</v>
+        <v>0.1069</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2589</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.4489</v>
+        <v>-6.8116</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1213</v>
+        <v>-4.6316</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3277</v>
+        <v>-2.1799</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8845</v>
@@ -2170,13 +2170,13 @@
         <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2298</v>
+        <v>0.4076</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1219</v>
+        <v>0.3678</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1079</v>
+        <v>0.0398</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2583</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-17.939</v>
+        <v>-17.9389</v>
       </c>
       <c r="E23" t="n">
-        <v>4.3337</v>
+        <v>4.333800000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-22.2727</v>
+        <v>-22.2726</v>
       </c>
       <c r="G23" t="n">
         <v>-8.3264</v>
@@ -2248,13 +2248,13 @@
         <v>12.0436</v>
       </c>
       <c r="S23" t="n">
-        <v>3.705699999999999</v>
+        <v>3.7057</v>
       </c>
       <c r="T23" t="n">
-        <v>2.0893</v>
+        <v>2.0894</v>
       </c>
       <c r="U23" t="n">
-        <v>1.6164</v>
+        <v>1.6165</v>
       </c>
       <c r="V23" t="n">
         <v>-2.201</v>
